--- a/セリフ編集/その他セリフ/04-挑戦試合.xlsx
+++ b/セリフ編集/その他セリフ/04-挑戦試合.xlsx
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_NO_LINES.normal[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_NO_LINES.standard[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,12 +655,12 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[1]</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[1]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="3">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_NO_LINES.normal[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_NO_LINES.standard[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,12 +687,12 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal[2]</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">standard[2]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">標準</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="3">
